--- a/output/2026-09-06_07_Slovenia_Savinjska_Metalworking_Lavorazioni_Metalliche.xlsx
+++ b/output/2026-09-06_07_Slovenia_Savinjska_Metalworking_Lavorazioni_Metalliche.xlsx
@@ -490,7 +490,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Verificato via ricerca web (Bizi.si, CompanyWall.si, sito ufficiale inpos.eu). Azienda attiva dal 1990, sede confermata Opekarniška cesta 2, Celje. Sito conferma reparto 'sesalniki industrijski'.</t>
+          <t>Verificato via ricerca web (Bizi.si, CompanyWall.si, sito ufficiale inpos.eu). Azienda attiva dal 1990, sede confermata Opekarniška cesta 2, Celje. Sito conferma reparto 'sesalniki industrijski'. [DUPLICATO — vedi anche: 2026-09-06_03_Slovenia_Koroska_Utensilerie_e_Macchine_Utensili.xlsx]</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -527,7 +527,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Verificato via ricerca web (Bizi.si, CompanyWall.si, sito ufficiale). Prosegue attività del predecessore Ivan Šrot s.p. (dal 1997), pioniere sistemi di aspirazione centralizzata nella zona di Celje.</t>
+          <t>Verificato via ricerca web (Bizi.si, CompanyWall.si, sito ufficiale). Prosegue attività del predecessore Ivan Šrot s.p. (dal 1997), pioniere sistemi di aspirazione centralizzata nella zona di Celje. [DUPLICATO — vedi anche: 2026-09-06_05_Slovenia_Savinjska_Depolverazione_Trattamento_aria.xlsx]</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -601,7 +601,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Verificato via ricerca web (CompanyWall.si, sito ufficiale). Attivo dal 2014, conferma vendita aspiratori industriali Makita e Lavor.</t>
+          <t>Verificato via ricerca web (CompanyWall.si, sito ufficiale). Attivo dal 2014, conferma vendita aspiratori industriali Makita e Lavor. [DUPLICATO — vedi anche: 2026-09-06_06_Slovenia_Savinjska_Utensilerie_e_Macchine_Utensili.xlsx]</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -638,7 +638,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>ATTENZIONE - discrepanza rispetto al nominativo grezzo: la ricerca web indica che il punto vendita/servizio Kärcher di Trnoveljska cesta 4a, Celje è gestito da 'Intercom Celje d.o.o.' (trgovina ASO), NON da 'Elesprom' (azienda distinta con sede a Maribor, Limbuška cesta 79). Ragione sociale corretta in base al riscontro; indirizzo e telefono confermati.</t>
+          <t>ATTENZIONE - discrepanza rispetto al nominativo grezzo: la ricerca web indica che il punto vendita/servizio Kärcher di Trnoveljska cesta 4a, Celje è gestito da 'Intercom Celje d.o.o.' (trgovina ASO), NON da 'Elesprom' (azienda distinta con sede a Maribor, Limbuška cesta 79). Ragione sociale corretta in base al riscontro; indirizzo e telefono confermati. [DUPLICATO — vedi anche: 2026-09-05_23_Slovenia_Podravska_Depolverazione_Trattamento_aria.xlsx]</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -675,7 +675,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Verificato come distributore Delfin in Slovenia (sito ufficiale, strojnistvo.com). Sede reale individuata via Bizi.si/AJPES: Zgornje Bitnje 344, Žabnica (Kranj) - diversa dall'ipotesi 'area Ljubljana' della lista grezza. Copertura diretta della zona Savinjska non confermata da fonte specifica ma presunta in quanto distributore unico nazionale del marchio. Telefono ed email non reperiti, lasciati vuoti.</t>
+          <t>Verificato come distributore Delfin in Slovenia (sito ufficiale, strojnistvo.com). Sede reale individuata via Bizi.si/AJPES: Zgornje Bitnje 344, Žabnica (Kranj) - diversa dall'ipotesi 'area Ljubljana' della lista grezza. Copertura diretta della zona Savinjska non confermata da fonte specifica ma presunta in quanto distributore unico nazionale del marchio. Telefono ed email non reperiti, lasciati vuoti. [DUPLICATO — vedi anche: 2026-09-06_05_Slovenia_Savinjska_Depolverazione_Trattamento_aria.xlsx]</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -749,7 +749,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Verificato via sito ufficiale (pagine prodotto Nederman SmartFilter, ventilatori industriali serie N, odsesovanje pri viru).</t>
+          <t>Verificato via sito ufficiale (pagine prodotto Nederman SmartFilter, ventilatori industriali serie N, odsesovanje pri viru). [DUPLICATO — vedi anche: 2026-09-06_05_Slovenia_Savinjska_Depolverazione_Trattamento_aria.xlsx]</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -860,7 +860,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Verificato via Bizi.si, sito ufficiale e Facebook. Azienda leader slovena in filtrazione dal 1990, con figure dedicate a 'industrial dust extraction'.</t>
+          <t>Verificato via Bizi.si, sito ufficiale e Facebook. Azienda leader slovena in filtrazione dal 1990, con figure dedicate a 'industrial dust extraction'. [DUPLICATO — vedi anche: 2026-09-06_01_Slovenia_Podravska_Metalworking_Lavorazioni_Metalliche.xlsx]</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -897,7 +897,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Verificato via sito ufficiale, itis.si e Bizi.si.</t>
+          <t>Verificato via sito ufficiale, itis.si e Bizi.si. [DUPLICATO — vedi anche: 2026-09-05_23_Slovenia_Podravska_Depolverazione_Trattamento_aria.xlsx]</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -934,7 +934,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Verificato via sito ufficiale (pagina 'industrijska filtracija'). Telefono ed email non reperiti nei risultati di ricerca, lasciati vuoti come da lista grezza.</t>
+          <t>Verificato via sito ufficiale (pagina 'industrijska filtracija'). Telefono ed email non reperiti nei risultati di ricerca, lasciati vuoti come da lista grezza. [DUPLICATO — vedi anche: 2026-09-06_05_Slovenia_Savinjska_Depolverazione_Trattamento_aria.xlsx]</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -971,7 +971,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Verificato via AJPES, Bizi.si e sito ufficiale. Azienda con quasi 70 anni di tradizione, 48 dipendenti, rating A+ 2026.</t>
+          <t>Verificato via AJPES, Bizi.si e sito ufficiale. Azienda con quasi 70 anni di tradizione, 48 dipendenti, rating A+ 2026. [DUPLICATO — vedi anche: 2026-09-06_05_Slovenia_Savinjska_Depolverazione_Trattamento_aria.xlsx]</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">

--- a/output/2026-09-06_07_Slovenia_Savinjska_Metalworking_Lavorazioni_Metalliche.xlsx
+++ b/output/2026-09-06_07_Slovenia_Savinjska_Metalworking_Lavorazioni_Metalliche.xlsx
@@ -569,7 +569,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (07/09/2026)</t>
         </is>
       </c>
     </row>
@@ -717,7 +717,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (07/09/2026)</t>
         </is>
       </c>
     </row>
@@ -791,7 +791,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (07/09/2026)</t>
         </is>
       </c>
     </row>
@@ -828,7 +828,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (07/09/2026)</t>
         </is>
       </c>
     </row>
@@ -1013,7 +1013,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (07/09/2026)</t>
         </is>
       </c>
     </row>
